--- a/construction_template/data/templates_blank/defect_improvement.xlsx
+++ b/construction_template/data/templates_blank/defect_improvement.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
-    <t xml:space="preserve">   任泰技術顧問有限公司</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">█施工抽查</t>
@@ -47,7 +47,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">111</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -55,7 +55,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年度西區水利建造物檢修改善及災後淤土、樹木復原及設施搶修預約維護工程</t>
+      <t xml:space="preserve"/>
     </r>
   </si>
   <si>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">監造單位</t>
   </si>
   <si>
-    <t xml:space="preserve">任泰技術顧問有限公司</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">發現日期</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">改善單位</t>
   </si>
   <si>
-    <t xml:space="preserve">逸峰營造有限公司</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">登錄編號</t>
@@ -90,7 +90,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">1.</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -98,7 +98,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">改善位置：第</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -107,7 +107,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -115,7 +115,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">次通報單</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -124,7 +124,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">-</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -132,7 +132,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">雙溪</t>
+      <t xml:space="preserve"/>
     </r>
   </si>
   <si>

--- a/construction_template/data/templates_blank/defect_improvement.xlsx
+++ b/construction_template/data/templates_blank/defect_improvement.xlsx
@@ -599,7 +599,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>

--- a/construction_template/data/templates_blank/defect_improvement.xlsx
+++ b/construction_template/data/templates_blank/defect_improvement.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">█施工抽查</t>
@@ -40,23 +40,7 @@
     <t xml:space="preserve">工程名稱</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">文件編號</t>
@@ -65,7 +49,7 @@
     <t xml:space="preserve">監造單位</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">發現日期</t>
@@ -77,63 +61,13 @@
     <t xml:space="preserve">改善單位</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">登錄編號</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
+    <t/>
   </si>
   <si>
     <r>

--- a/construction_template/data/templates_blank/defect_improvement.xlsx
+++ b/construction_template/data/templates_blank/defect_improvement.xlsx
@@ -82,7 +82,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">不符情形：工區施作後環境未清理。</t>
@@ -101,7 +101,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">改善追蹤：要求施工人員立即清除混凝土修復面上既有鋼釘。</t>
@@ -123,7 +123,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年  月  日</t>
@@ -182,12 +182,12 @@
     </font>
     <font>
       <sz val="16"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -198,7 +198,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
